--- a/design/数值体系_v1.0.xlsx
+++ b/design/数值体系_v1.0.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2114,6 +2114,82 @@
       <c r="E73" s="6" t="inlineStr">
         <is>
           <t>上传回合数 = CEIL(缓存格数 / 10);每回合成本见动作成本·电量/信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>回收进程·倒数步数</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>步</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>本轮新增(苏丹类比①)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>溯源≥90(非演出)激活;每动作−1;抵达=90档真掷(教学局降档/B局自救链);扑空或擦过后重置5步</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>回收进程·判定</t>
+        </is>
+      </c>
+      <c r="B75">
+        <f>90档遭遇</f>
+        <v/>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>d100</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>本轮新增(苏丹类比①)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>复用 c90=55,判定不加码;死亡最后一步由玩家亲手按「面对」</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>断连仪式·长按时长</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>本轮新增(苏丹类比②)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>触摸长按拔线;松手取消;键盘 Enter 为退化路径;纯呈现,零数值</t>
         </is>
       </c>
     </row>
